--- a/_build/out/workbook.xlsx
+++ b/_build/out/workbook.xlsx
@@ -438,10 +438,10 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>9 / 14종</t>
+          <t>11 / 14종</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -2689,7 +2689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H24"/>
+  <dimension ref="B2:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.2" customWidth="1" min="1" max="1"/>
@@ -2713,7 +2713,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="22" t="inlineStr">
         <is>
-          <t>분자식 14종 중 교과서·학습 핵심 9종 (연노란색) · 초록 글자 = 원소, 남색 글자 = 화합물</t>
+          <t>분자식 14종 중 교과서·학습 핵심 11종 (연노란색) · 초록 글자 = 원소, 남색 글자 = 화합물</t>
         </is>
       </c>
     </row>
@@ -3106,35 +3106,35 @@
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="B16" s="29" t="n">
+      <c r="B16" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="C16" s="30" t="inlineStr">
+      <c r="C16" s="25" t="inlineStr">
         <is>
           <t>H₂O₂</t>
         </is>
       </c>
-      <c r="D16" s="29" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>H2O2</t>
         </is>
       </c>
-      <c r="E16" s="46" t="inlineStr">
+      <c r="E16" s="44" t="inlineStr">
         <is>
           <t>과산화 수소</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F16" s="45" t="inlineStr">
         <is>
           <t>화합물</t>
         </is>
       </c>
-      <c r="G16" s="31" t="inlineStr">
-        <is>
-          <t>확장</t>
-        </is>
-      </c>
-      <c r="H16" s="32" t="inlineStr">
+      <c r="G16" s="26" t="inlineStr">
+        <is>
+          <t>핵심</t>
+        </is>
+      </c>
+      <c r="H16" s="37" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -3154,7 +3154,7 @@
           <t>SO2</t>
         </is>
       </c>
-      <c r="E17" s="47" t="inlineStr">
+      <c r="E17" s="46" t="inlineStr">
         <is>
           <t>이산화 황</t>
         </is>
@@ -3189,7 +3189,7 @@
           <t>NO2</t>
         </is>
       </c>
-      <c r="E18" s="46" t="inlineStr">
+      <c r="E18" s="47" t="inlineStr">
         <is>
           <t>이산화 질소</t>
         </is>
@@ -3211,35 +3211,35 @@
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="B19" s="33" t="n">
+      <c r="B19" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="C19" s="34" t="inlineStr">
+      <c r="C19" s="25" t="inlineStr">
         <is>
           <t>C₆H₁₂O₆</t>
         </is>
       </c>
-      <c r="D19" s="33" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>C6H12O6</t>
         </is>
       </c>
-      <c r="E19" s="47" t="inlineStr">
+      <c r="E19" s="44" t="inlineStr">
         <is>
           <t>포도당</t>
         </is>
       </c>
-      <c r="F19" s="18" t="inlineStr">
+      <c r="F19" s="45" t="inlineStr">
         <is>
           <t>화합물</t>
         </is>
       </c>
-      <c r="G19" s="35" t="inlineStr">
-        <is>
-          <t>확장</t>
-        </is>
-      </c>
-      <c r="H19" s="36" t="inlineStr">
+      <c r="G19" s="26" t="inlineStr">
+        <is>
+          <t>핵심</t>
+        </is>
+      </c>
+      <c r="H19" s="37" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -3248,7 +3248,7 @@
     <row r="21" ht="18" customHeight="1">
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>※ 연노란색 = 교과서 Ⅳ단원에 화학식이 실제로 나오는 물질. 141쪽 = 그림 Ⅳ-3, 153쪽 = 분자의 화학식.</t>
+          <t>※ 연노란색 = 학습 핵심 11종(학습 사이트 '교과서·학습 핵심만' 범위). 교과서 확인 쪽수가 적힌 물질은 Ⅳ단원에 화학식이 실제로 나옵니다. 141쪽 = 그림 Ⅳ-3, 153쪽 = 분자의 화학식.</t>
         </is>
       </c>
     </row>
@@ -3262,23 +3262,31 @@
     <row r="23" ht="18" customHeight="1">
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>※ 질소(N₂) · 과산화 수소(H₂O₂) · 이산화 황(SO₂) · 이산화 질소(NO₂) · 포도당(C₆H₁₂O₆)은 이 단원에 나오지 않지만 수업에서 자주 다루는 확장 항목입니다.</t>
+          <t>※ 이 단원에 나오지 않지만 수업에서 자주 다루는 물질 — 학습 핵심: 과산화 수소(H₂O₂) · 포도당(C₆H₁₂O₆)  /  확장: 질소(N₂) · 이산화 황(SO₂) · 이산화 질소(NO₂)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="B24" s="20" t="inlineStr">
         <is>
+          <t>※ 4쪽 학습지(PDF)의 분자식 칸에는 핵심·확장 구분 없이 14종이 모두 실려 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="B25" s="20" t="inlineStr">
+        <is>
           <t>※ '입력용 표기'는 학습 사이트에서 답을 칠 때 쓰는 형태입니다. 숫자는 자동으로 아래첨자가 됩니다. 예) H2O → H₂O</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="B22:H22"/>
     <mergeCell ref="B21:H21"/>
     <mergeCell ref="B24:H24"/>
     <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B25:H25"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B23:H23"/>
   </mergeCells>
